--- a/templates/Stage 3 - Scope.xlsx
+++ b/templates/Stage 3 - Scope.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Workflow Map" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Data Inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Integration Requirements" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Constraints &amp; Assumptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workflow Map" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Inventory" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Integration Requirements" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Constraints &amp; Assumptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1855,7 +1855,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="75" customHeight="1">
+    <row r="2" ht="90" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>Framework</t>
@@ -1863,12 +1863,12 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LangGraph — agent orchestration framework for defining the workflow as a state machine with nodes and edges</t>
+          <t>Agent orchestration framework — defines the workflow as a flow of actions with memory passed between them</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>LangGraph ≥0.2 (Python) — requires langgraph package</t>
+          <t>Whichever framework your team has chosen (see Stage 4: Choose a Platform). Typical minimums: a recent stable release, Python 3.11+ or the platform's equivalent runtime.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Core dependency. The workflow map steps translate into LangGraph nodes in Stage 4. Each AUTOMATE step becomes a tool-calling node, each HIL step becomes an interrupt-before checkpoint. Install via pip install langgraph.</t>
+          <t>Core dependency. The workflow map steps translate into flow actions in Stage 4. Each AUTOMATE step becomes a tool-calling action, each HIL step becomes an HIL checkpoint. Installation / setup instructions depend on the chosen platform — see the platform cheat sheet.</t>
         </is>
       </c>
     </row>
@@ -1895,12 +1895,12 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LangChain — tool wrappers and abstractions for data source integrations</t>
+          <t>Tool wrapping layer — standardised interface for data source integrations</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>LangChain ≥0.3 (Python) — requires langchain and langchain-community packages</t>
+          <t>Platform-dependent — typically provided by the chosen agent framework or a thin wrapper you write per data source</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Used for tool abstractions that wrap each data source API. Provides standardised interfaces for the agent to call Salesforce, Zendesk, Mixpanel, and Slack APIs as tools. Install via pip install langchain langchain-community.</t>
+          <t>Used to wrap each data source API so the agent can call Salesforce, Zendesk, Mixpanel, and Slack as tools. Most platforms provide a tool abstraction layer; otherwise write a thin wrapper module per source.</t>
         </is>
       </c>
     </row>
@@ -1927,12 +1927,12 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Anthropic SDK — Claude API access for synthesis / summarisation / report generation</t>
+          <t>Language model API access for synthesis / summarisation / report generation</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Anthropic Python SDK ≥0.39 (anthropic package), Claude model (claude-sonnet-4-20250514 or later recommended)</t>
+          <t>A capable general-purpose LLM available via API. Use whichever model your team has approved — match capability to task (a stronger model for synthesis, a cheaper model for structured extraction where appropriate).</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Required for Steps 5, 8, 9, 10, and 11 where the agent synthesises data, applies contextual judgement, or generates narrative text. API key must be provisioned and stored securely. Consider claude-sonnet-4-20250514 for cost-efficiency on data retrieval nodes, Claude Opus for synthesis and report generation nodes.</t>
+          <t>Required for Steps 5, 8, 9, 10, and 11 where the agent synthesises data, applies contextual judgement, or generates narrative text. API credentials must be provisioned and stored securely. Consider a lighter model for data-retrieval actions and a stronger model for synthesis / report generation.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>All data source credentials (Salesforce OAuth tokens, Zendesk API key, Mixpanel API secret, Slack bot token, Anthropic API key) must be stored securely and never hardcoded. For local development, .env file with python-dotenv is acceptable. For production, use a secrets manager. Document the required environment variables in the project README.</t>
+          <t>All data source credentials (Salesforce OAuth tokens, Zendesk API key, Mixpanel API secret, Slack bot token, LLM provider API key) must be stored securely and never hardcoded. For local development, .env file with python-dotenv is acceptable. For production, use a secrets manager. Document the required environment variables in the project README.</t>
         </is>
       </c>
     </row>
@@ -2207,7 +2207,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="75" customHeight="1">
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Infrastructure</t>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Python runtime environment</t>
+          <t>Runtime environment</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Python ≥3.11 with virtual environment (venv or conda)</t>
+          <t>Python 3.11+ (or the runtime your chosen platform expects) with isolated dependencies (venv, conda, container, or platform-managed environment)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>All framework dependencies (LangGraph, LangChain, Anthropic SDK) require Python 3.11+. Use a virtual environment to isolate dependencies. A requirements.txt or pyproject.toml should pin all dependency versions.</t>
+          <t>The chosen agent framework and LLM provider SDK typically require Python 3.11+. Use a virtual environment or container to isolate dependencies. A requirements.txt / pyproject.toml / lockfile should pin all dependency versions.</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2247,12 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>LangGraph checkpointing — persistence for HIL interrupt/resume workflow</t>
+          <t>Checkpointing / state persistence — durable pause-and-resume for HIL workflow</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>LangGraph MemorySaver (development) or SqliteSaver / PostgresSaver (production)</t>
+          <t>The agent framework's checkpointing layer — development and production options depend on your platform (typical progression: in-memory for development, a durable store such as SQLite or Postgres for production)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>LangGraph's interrupt-before mechanism (used for HIL steps) requires a checkpointer to persist state between human review cycles. MemorySaver is fine for development; production needs durable storage. This is a Stage 5 build decision but should be planned for now.</t>
+          <t>The HIL checkpoints (used for HIL steps) require a persistence layer so memory is preserved between human review cycles. In-memory persistence is fine for development; production needs durable storage. This is a Stage 5 build decision but should be planned for now.</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>If an account has multiple active products, the health scoring step (Step 9) would produce a single score that conflates the health of different products — a healthy Product A could mask a failing Product B. The engagement assessment (Step 7) would need to evaluate and weight each product separately, the state schema in Stage 4 would need a product-level loop, and the scoring rubric in Stage 5 would need per-product dimensions.</t>
+          <t>If an account has multiple active products, the health scoring step (Step 9) would produce a single score that conflates the health of different products — a healthy Product A could mask a failing Product B. The engagement assessment (Step 7) would need to evaluate and weight each product separately, the memory schema in Stage 4 would need a product-level loop, and the scoring rubric in Stage 5 would need per-product dimensions.</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (workflow map Steps 7 and 9 would need product-level sub-steps), Stage 4 (state schema needs a product-level loop within the account-level workflow), Stage 5 (scoring rubric config needs per-product dimensions and a product-weighting strategy)</t>
+          <t>Stage 3 (workflow map Steps 7 and 9 would need product-level sub-steps), Stage 4 (memory schema needs a product-level loop within the account-level workflow), Stage 5 (scoring rubric config needs per-product dimensions and a product-weighting strategy)</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (date range parameters in Steps 2-4 need to account for data freshness lag), Stage 5 (data retrieval nodes need configurable date ranges with freshness checks)</t>
+          <t>Stage 3 (date range parameters in Steps 2-4 need to account for data freshness lag), Stage 5 (data retrieval actions need configurable date ranges with freshness checks)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Stage 5 (data retrieval node for Zendesk may need a staleness buffer — e.g. only evaluate tickets closed ≥48 hours ago for CSAT completeness)</t>
+          <t>Stage 5 (data retrieval action for Zendesk may need a staleness buffer — e.g. only evaluate tickets closed ≥48 hours ago for CSAT completeness)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (boundary tags for Steps 1-4 may need revision), Stage 4 (manual steps cannot become LangGraph nodes — they become external dependencies with wait states), Stage 5 (build scope shrinks if data retrieval is manual)</t>
+          <t>Stage 3 (boundary tags for Steps 1-4 may need revision), Stage 4 (manual steps cannot become flow actions — they become external dependencies with wait states), Stage 5 (build scope shrinks if data retrieval is manual)</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (if reversed, Step 12 boundary would change from MANUAL to AUTOMATE or HIL, requiring a new approval checkpoint), Stage 4 (would need a confirmation node with explicit human approval before send), Stage 5 (would need email/Slack integration with send permissions)</t>
+          <t>Stage 3 (if reversed, Step 12 boundary would change from MANUAL to AUTOMATE or HIL, requiring a new approval checkpoint), Stage 4 (would need a confirmation action with explicit human approval before send), Stage 5 (would need email/Slack integration with send permissions)</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Stage 5 (config/scoring_rubric.yaml would need versioning — each report must record which config version was used), Stage 3 (if criteria change frequently, the constraint should be relaxed and the workflow should include a config version check at startup)</t>
+          <t>Stage 5 (scoring rubric config file would need versioning — each report must record which config version was used), Stage 3 (if criteria change frequently, the constraint should be relaxed and the workflow should include a config version check at startup)</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Stage 4 (state schema would need account-level isolation, the graph would need a batch orchestration layer above the single-account workflow), Stage 5 (rate limiting would need global coordination across concurrent runs, checkpointing would need account-level namespacing)</t>
+          <t>Stage 4 (memory schema would need account-level isolation, the flow would need a batch orchestration layer above the single-account workflow), Stage 5 (rate limiting would need global coordination across concurrent runs, checkpointing would need account-level namespacing)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Stage 3 (if Slack coverage is too sparse, consider adding alternative sentiment sources — e.g. email tone analysis, NPS survey data), Stage 5 (the Slack retrieval node may need to search broader date ranges or additional channels to increase coverage)</t>
+          <t>Stage 3 (if Slack coverage is too sparse, consider adding alternative sentiment sources — e.g. email tone analysis, NPS survey data), Stage 5 (the Slack retrieval action may need to search broader date ranges or additional channels to increase coverage)</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
